--- a/requirement_checks/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
+++ b/requirement_checks/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -61,7 +67,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,16 +81,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFDDC1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -106,11 +117,44 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,16 +168,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -568,13 +623,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="156" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -587,9 +642,21 @@
           <t>https://github.com/CSUBioGroup/2OMe-LM</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py, predict.py</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>data/mydataset.py, cv_train.py, predict.py, train.py, models/LM_2OME.py, utils/binary_metrics.py, utils/config.py, utils/WarmupLR.py</t>
@@ -597,21 +664,20 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3" ht="156" customHeight="1">
+          <t>The repository contains executable code that tokenizes RNA sequences (including U-&gt;T normalization and k-mer segmentation) using a HuggingFace tokenizer before model processing.</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7270</v>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -624,9 +690,21 @@
           <t>https://github.com/hustvl/4DLangVGGT</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>y, x = torch.meshgrid(torch.arange(0, self.image_height), torch.arange(0, self.image_width)); point_feature_small = lang_feat[seg[1:2]].squeeze(0); concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>utils/demo_dataloader.py, preprocess/generate_vggttoken.py, scripts/infer.sh, inference.py, train.py, head/langhead.py, models/langvggt.py, utils/misc.py, utils/utils.py, streamvggt/heads/camera_head.py</t>
@@ -634,19 +712,18 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 4000}, for model=gpt-5-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="156" customHeight="1">
+          <t>The repo includes executable data pipeline code that prepares and collates features and tokens into model-ready inputs, matching the input construction/prompting category.</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>15451</v>
+      </c>
+    </row>
+    <row r="4" ht="97.5" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
         </is>
@@ -663,7 +740,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>response = self.client.chat.completions.create(model=self.model, messages=[{"role": "user", "content": prompt}],; with open(taghelper_path, "w", encoding="utf-8") as f:
+    f.write(TAGHELPER_CODE); Automation Agent → Builds playable Unity scenes programmatically.</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py, gpt_interface.py</t>
@@ -671,21 +753,20 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="156" customHeight="1">
+          <t>The repository files shown do not implement tokenization, data cleaning/deduplication, or non-trivial prompt/input construction; they only include Unity script generation and a simple API call wrapper.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -698,9 +779,21 @@
           <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py, src/JointDataset.py</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>drug = drug[variable_drug].fillna(drug.mean()); Essentiality.columns = [col.split(" ")[0] for col in Essentiality.columns]; self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py, src/baseline_VAE.py, src/DeepVul.py, src/model.py, src/run.py, src/utils.py</t>
@@ -708,21 +801,20 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="156" customHeight="1">
+          <t>There is non-trivial preprocessing code for filtering/cleaning (column renaming, variable feature selection, NaN imputation, index intersection) and normalization used to construct datasets.</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8464</v>
+      </c>
+    </row>
+    <row r="6" ht="117" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -735,9 +827,21 @@
           <t>https://github.com/cchihyu/A2D2E</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>.build_prompt &lt;- function(dat, x_target) {; resp &lt;- openai::create_chat_completion(model = object$model, temperature = object$temperature, messages = list(; pairs &lt;- apply(cbind(X, dat$y), 1, function(row) { paste0("((", paste(sprintf("%.6f", row[1:(length(row)-1)]), collapse = ","), "),", sprintf("%.6f", row[length(row)]), ")") })</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
@@ -745,13 +849,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
+          <t>There is executable prompt-building and wrapper code (GPT_agent.R) that constructs LLM prompts and parses predictions.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>16961</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -829,20 +932,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -864,20 +967,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -899,22 +1002,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -934,20 +1037,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -969,66 +1072,66 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>5/5 (100%)</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>4/5 (80%)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Token Usage per Model</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Input Tokens</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Output Tokens</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Total Tokens</t>
         </is>
@@ -1041,21 +1144,21 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46,551</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5,441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51,992</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1169,21 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46,551</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4,441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50,992</t>
         </is>
       </c>
     </row>
@@ -1091,21 +1194,21 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46,551</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8,229</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54,780</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1260,153 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>2OMe-LM: predicting 2′-O-methylation sites in human RNA using a pre-trained RNA language model</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>predict.py</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>4DLangVGGT: 4D Language-Visual Geometry Grounded Transformer</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>src/JointDataset.py</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1188,133 +1437,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="10" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Skipped (non-GitHub)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Skipped (non-GitHub)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Coverage (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <f>4/5*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>LLM Token Usage</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Model / Deployment</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>gpt-5-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Requests</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Coverage (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>0/5*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>LLM Token Usage</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Model / Deployment</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>gpt-5-2025-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Requests</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>46,551</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>5,441</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>51,992</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1645,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="156" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1415,9 +1664,21 @@
           <t>https://github.com/CSUBioGroup/2OMe-LM</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>tokenization, prompting</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py, predict.py</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>data/mydataset.py, cv_train.py, predict.py, train.py, models/LM_2OME.py, utils/binary_metrics.py, utils/config.py, utils/WarmupLR.py</t>
@@ -1425,21 +1686,20 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-mini-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3" ht="156" customHeight="1">
+          <t>Executable code in data/mydataset.py and predict.py performs tokenization and input-construction pipelines (SpliceBERT tokenizer + k-mer/Word2Vec features), so preprocessing exists.</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7146</v>
+      </c>
+    </row>
+    <row r="3" ht="195" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1452,9 +1712,24 @@
           <t>https://github.com/hustvl/4DLangVGGT</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py, scripts/infer.sh</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>streamvggt.inference_long_video(image_files, save_dir=save_dir, keys=keys, mode=args.mode, max_num=args.max_num); streamvggt_path = os.path.join(self.img_root, cat, self.streamvggt_token_root, key + '.npy')
+streamvggt_info = np.load(streamvggt_path, allow_pickle=True).item(); all_aggregated_tokens[pos].append(torch.from_numpy(item[key][pos]))
+concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)
+collated['aggregated_tokens_list'] = aggregated_tokens_list</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>utils/demo_dataloader.py, preprocess/generate_vggttoken.py, scripts/infer.sh, inference.py, train.py, head/langhead.py, models/langvggt.py, utils/misc.py, utils/utils.py, streamvggt/heads/camera_head.py</t>
@@ -1462,21 +1737,20 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 4000}, for model=gpt-5-mini-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="156" customHeight="1">
+          <t>generate_vggttoken.py produces token .npy files via StreamVGGT inference and demo_dataloader.py loads and collates those tokens into input tensors, which qualifies as an executable tokenization/preprocessing pipeline.</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>14803</v>
+      </c>
+    </row>
+    <row r="4" ht="253.5" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1489,9 +1763,29 @@
           <t>https://github.com/yxwan123/UniGen</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>blue_pipeline.py, gpt_interface.py</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>import os
+import json
+import re
+from gpt_interface import GPT4Bot # MLLM backbone (e.g., GPT-4.1); response = self.client.chat.completions.create(
+                    model=self.model,
+                    messages=[{"role": "user", "content": prompt}],
+                    max_tokens=4096,
+                    temperature=0,; Each agent builds upon the structured output of the previous one,
+forming a complete end-to-end pipeline for automated 3D game generation.</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py, gpt_interface.py</t>
@@ -1499,21 +1793,20 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-mini-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="156" customHeight="1">
+          <t>There is executable code for prompting (a GPT wrapper and a multi-agent pipeline that composes/uses prompts to generate project files), so prompting-related preprocessing exists.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="5" ht="97.5" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1526,9 +1819,21 @@
           <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py, src/JointDataset.py</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>drug = drug[variable_drug].fillna(drug.mean()); with open("../data/top1000_variable_genes.txt", 'r') as file:\n        var_features = file.read().splitlines(); self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py, src/baseline_VAE.py, src/DeepVul.py, src/model.py, src/run.py, src/utils.py</t>
@@ -1536,21 +1841,20 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-mini-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="156" customHeight="1">
+          <t>Files implement non-trivial preprocessing: selecting variable features, dropping/ filling missing columns, assembling per-cell tensors, and normalizing expression data, so a filtering/cleaning pipeline exists.</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8297</v>
+      </c>
+    </row>
+    <row r="6" ht="292.5" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1563,9 +1867,30 @@
           <t>https://github.com/cchihyu/A2D2E</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>.build_prompt &lt;- function(dat, x_target) {; sprintf(paste0(
+    "You are given training data in the form of ((x1,...,xd),y):\n%s\n\n",
+    "Question: What is your prediction of y at x = (%s)?\n",
+    "Return only a single numerical scalar with no explanation."; resp &lt;- openai::create_chat_completion(
+      model = object$model, temperature = object$temperature,
+      messages = list(
+        list(role = "system", content = object$system_prompt),
+        list(role = "user",   content = user_prompt)
+      )
+    )</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
@@ -1573,13 +1898,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-mini-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
+          <t>GPT_agent.R implements a full prompt-construction pipeline (.build_prompt) and uses create_chat_completion to query a model, which clearly matches the prompting wrappers / input construction category.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>16706</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1592,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1629,7 +1953,233 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>2OMe-LM: predicting 2′-O-methylation sites in human RNA using a pre-trained RNA language model</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>predict.py</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>4DLangVGGT: 4D Language-Visual Geometry Grounded Transformer</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>preprocess/generate_vggttoken.py</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/preprocess/generate_vggttoken.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>scripts/infer.sh</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/scripts/infer.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>blue_pipeline.py</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>gpt_interface.py</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/gpt_interface.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>src/JointDataset.py</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1660,133 +2210,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="10" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Skipped (non-GitHub)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Skipped (non-GitHub)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Coverage (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <f>5/5*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>LLM Token Usage</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Model / Deployment</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>gpt-5-mini-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Requests</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Coverage (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>0/5*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>LLM Token Usage</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Model / Deployment</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>gpt-5-mini-2025-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Requests</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>46,551</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>4,441</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>50,992</t>
         </is>
       </c>
     </row>
@@ -1868,13 +2418,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="156" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1887,9 +2437,21 @@
           <t>https://github.com/CSUBioGroup/2OMe-LM</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py, predict.py</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); seq = ' '.join(list(seq.upper().replace("U", "T")))</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>data/mydataset.py, cv_train.py, predict.py, train.py, models/LM_2OME.py, utils/binary_metrics.py, utils/config.py, utils/WarmupLR.py</t>
@@ -1897,21 +2459,20 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-nano-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3" ht="156" customHeight="1">
+          <t>There is executable tokenization and input-construction code that builds model-ready inputs from RNA sequences.</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1924,9 +2485,21 @@
           <t>https://github.com/hustvl/4DLangVGGT</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>from streamvggt.models.streamvggt import StreamVGGT; streamvggt.inference_long_video(; save_dir = os.path.join(args.img_root, cat, 'streamvggt_token')</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>utils/demo_dataloader.py, preprocess/generate_vggttoken.py, scripts/infer.sh, inference.py, train.py, head/langhead.py, models/langvggt.py, utils/misc.py, utils/utils.py, streamvggt/heads/camera_head.py</t>
@@ -1934,21 +2507,20 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 4000}, for model=gpt-5-nano-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="156" customHeight="1">
+          <t>The repository includes non-trivial preprocessing/input-construction code (token generation and data loading) rather than purely training or inference scripts.</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>16848</v>
+      </c>
+    </row>
+    <row r="4" ht="58.5" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1961,9 +2533,21 @@
           <t>https://github.com/yxwan123/UniGen</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>blue_pipeline.py</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>from gpt_interface import GPT4Bot # MLLM backbone (e.g., GPT-4.1); TAGHELPER_CODE = '''using UnityEditor;; def CreateUIManagerGO()</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py, gpt_interface.py</t>
@@ -1971,21 +2555,20 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-nano-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="156" customHeight="1">
+          <t>The shown code implements a prompting/input-construction pipeline that leverages an LLM to generate and assemble Unity project components.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1998,9 +2581,21 @@
           <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>src/JointDataset.py, src/utils.py</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Essentiality = Essentiality[var_features].dropna(axis='columns'); with open("../data/top500_variable_drug.txt", 'r') as file:; self.data_exp = self.normalize_tensor_columns(self.data_exp)</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py, src/baseline_VAE.py, src/DeepVul.py, src/model.py, src/run.py, src/utils.py</t>
@@ -2008,21 +2603,20 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-nano-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="156" customHeight="1">
+          <t>There are executable preprocessing components (data filtering/cleaning and normalization) implemented in Python modules, not just training/inference scripts.</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8966</v>
+      </c>
+    </row>
+    <row r="6" ht="58.5" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2035,9 +2629,21 @@
           <t>https://github.com/cchihyu/A2D2E</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>You are given training data in the form of ((x1,...,xd),y):; Return only a single numerical scalar with no explanation.; openai::create_chat_completion</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
@@ -2045,13 +2651,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unexpected error: litellm.UnsupportedParamsError: ollama does not support parameters: {'max_completion_tokens': 2000}, for model=gpt-5-nano-2025-08-07. To drop these, set `litellm.drop_params=True` or for proxy:
-`litellm_settings:
- drop_params: true`
-</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
+          <t>GPT_agent.R implements a prompting wrapper, creating input prompts and handling API responses, i.e., an input-construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>17471</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2064,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2101,7 +2706,198 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>2OMe-LM: predicting 2′-O-methylation sites in human RNA using a pre-trained RNA language model</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>data/mydataset.py</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>predict.py</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>4DLangVGGT: 4D Language-Visual Geometry Grounded Transformer</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>preprocess/generate_vggttoken.py</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/preprocess/generate_vggttoken.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>blue_pipeline.py</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>src/JointDataset.py</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>GPT_agent.R</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2132,133 +2928,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="10" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Skipped (non-GitHub)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Skipped (non-GitHub)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Coverage (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <f>5/5*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>LLM Token Usage</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Model / Deployment</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>gpt-5-nano-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Requests</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Coverage (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>0/5*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>LLM Token Usage</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Model / Deployment</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>gpt-5-nano-2025-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Requests</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>46,551</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>8,229</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>54,780</t>
         </is>
       </c>
     </row>
